--- a/data/LMGB.xlsx
+++ b/data/LMGB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2025-27 PGDM 2nd Year\Ravinder sir\2025-27 TERM 5\Attendance sheet of term-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sritam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FB51A6-71B6-4B73-B437-580C5AFA06B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8257BC7-724C-4428-939C-DCA3939D2397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{463FB2F6-E5B4-4CCE-A9A7-042A6E3CBE50}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{463FB2F6-E5B4-4CCE-A9A7-042A6E3CBE50}"/>
   </bookViews>
   <sheets>
     <sheet name="LIST" sheetId="2" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="173">
   <si>
     <t>Roll No</t>
   </si>
@@ -555,13 +552,19 @@
   </si>
   <si>
     <t>pgdm25chaitanya_s@mdi.ac.in</t>
+  </si>
+  <si>
+    <t>25P055</t>
+  </si>
+  <si>
+    <t>Sritam Tripathy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,6 +583,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -621,18 +630,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -977,85 +980,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F2D6F1-197E-4F14-A64A-DBBDF11F42FF}">
-  <dimension ref="A1:C56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A56" si="0">A3+1</f>
+        <f t="shared" ref="A4:A57" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1067,592 +1070,604 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1661,6 +1676,7 @@
       <sortCondition ref="B1:B56"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B11">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
@@ -1671,122 +1687,122 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739FB103-D847-4D8B-8787-34CB1D081F87}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" style="4" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A56" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1797,892 +1813,892 @@
       <c r="C7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E30" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E31" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="E34" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E44" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E45" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E46" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E47" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E48" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E53" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E55" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="3" t="s">
         <v>167</v>
       </c>
     </row>
